--- a/Result/profitability/5475.xlsx
+++ b/Result/profitability/5475.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.55</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.14625</v>
+        <v>-0.002500000000000002</v>
       </c>
       <c r="N2" t="n">
-        <v>13.8575</v>
+        <v>17.21375</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>-0.05</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.1275</v>
+        <v>0.05374999999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>13.76125</v>
+        <v>17.88875</v>
       </c>
       <c r="O3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>-0.78</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.1625</v>
+        <v>-0.02500000000000001</v>
       </c>
       <c r="N4" t="n">
-        <v>12.58625</v>
+        <v>15.445</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.97</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.265</v>
+        <v>-0.13125</v>
       </c>
       <c r="N5" t="n">
-        <v>-2.341249999999999</v>
+        <v>0.1912499999999984</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.43</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.30375</v>
+        <v>-0.18625</v>
       </c>
       <c r="N6" t="n">
-        <v>-6.97</v>
+        <v>-5.075000000000001</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,13 +1264,13 @@
         <v>-0.24</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.335</v>
+        <v>-0.22875</v>
       </c>
       <c r="N7" t="n">
-        <v>-9.6325</v>
+        <v>-7.956250000000002</v>
       </c>
       <c r="O7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
         <v>1</v>
@@ -1282,7 +1282,7 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>-0.15</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.36625</v>
+        <v>-0.2775</v>
       </c>
       <c r="N8" t="n">
-        <v>-12.43</v>
+        <v>-11.3925</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1645,7 +1645,7 @@
         <v>0.28</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.3750000000000001</v>
+        <v>-0.375</v>
       </c>
       <c r="N10" t="n">
         <v>-15.49375</v>
@@ -1899,7 +1899,7 @@
         <v>0.58</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.05375000000000001</v>
+        <v>-0.05374999999999998</v>
       </c>
       <c r="N12" t="n">
         <v>-8.866250000000001</v>
@@ -2026,7 +2026,7 @@
         <v>-0.55</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.001250000000000015</v>
+        <v>-0.001250000000000001</v>
       </c>
       <c r="N13" t="n">
         <v>2.844999999999999</v>
@@ -9830,6 +9830,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>5475</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>511</v>
+      </c>
+      <c r="D75" t="n">
+        <v>324</v>
+      </c>
+      <c r="E75" t="n">
+        <v>187</v>
+      </c>
+      <c r="F75" t="n">
+        <v>36.62</v>
+      </c>
+      <c r="G75" t="n">
+        <v>121</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>23.66%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J75" t="n">
+        <v>121</v>
+      </c>
+      <c r="K75" t="n">
+        <v>121</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.04125</v>
+      </c>
+      <c r="N75" t="n">
+        <v>19.13625</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>1</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="X75" t="n">
+        <v>2.958333333333333</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>8.299999999999997</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.2930790960451977</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-8.916666666666668</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>20.26</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>1.238386308068459</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
